--- a/pregenereated_results/s2/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/pregenereated_results/s2/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -746,7 +746,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3814097435289841</v>
+        <v>0.3814097435289842</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
